--- a/data/50001532 - XEMORTIZ AMERICAS GOLD B.xlsx
+++ b/data/50001532 - XEMORTIZ AMERICAS GOLD B.xlsx
@@ -9065,7 +9065,7 @@
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46181.19875577546</v>
+        <v>46188.16859015047</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>314</v>
@@ -9126,7 +9126,7 @@
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46118.64740956019</v>
+        <v>46188.168568113426</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>143</v>
@@ -9177,7 +9177,7 @@
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46118.64740554398</v>
+        <v>46188.16856979167</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>143</v>
@@ -9228,7 +9228,7 @@
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46118.64740210648</v>
+        <v>46188.168570995374</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>143</v>
@@ -9279,7 +9279,7 @@
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46118.647399016205</v>
+        <v>46188.1685722338</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>143</v>
@@ -9330,7 +9330,7 @@
       </c>
       <c r="C141" s="10"/>
       <c r="D141" s="9">
-        <v>46118.64739414352</v>
+        <v>46188.16857356481</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>143</v>
